--- a/03_DateAndTime.xlsx
+++ b/03_DateAndTime.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{9CBA6948-8324-4744-92ED-92886B6749B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5E2B7B51-C35F-4661-B53F-5885861E7227}"/>
+    <workbookView minimized="1" xWindow="3732" yWindow="3732" windowWidth="17280" windowHeight="9960" xr2:uid="{5E2B7B51-C35F-4661-B53F-5885861E7227}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/03_DateAndTime.xlsx
+++ b/03_DateAndTime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f595840ab58673e5/Desktop/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CBA6948-8324-4744-92ED-92886B6749B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{9CBA6948-8324-4744-92ED-92886B6749B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{2815A17F-C57E-44F7-A0A0-46AC8E5A1D79}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3732" yWindow="3732" windowWidth="17280" windowHeight="9960" xr2:uid="{5E2B7B51-C35F-4661-B53F-5885861E7227}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5E2B7B51-C35F-4661-B53F-5885861E7227}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B11" s="3">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46109</v>
       </c>
       <c r="C11">
         <f ca="1">YEAR(B11)</f>
@@ -1876,11 +1876,11 @@
       </c>
       <c r="B12" s="3">
         <f ca="1">TODAY()-1</f>
-        <v>46076</v>
+        <v>46108</v>
       </c>
       <c r="C12">
         <f ca="1">MONTH(B12)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
@@ -1892,11 +1892,11 @@
       </c>
       <c r="B13" s="3">
         <f ca="1">TODAY()+1</f>
-        <v>46078</v>
+        <v>46110</v>
       </c>
       <c r="C13">
         <f ca="1">DAY(B13)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C17">
         <f ca="1">DATEDIF(B17,TODAY(),"d")</f>
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="D17" t="s">
         <v>35</v>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="C18">
         <f ca="1">NETWORKDAYS(B18,TODAY())</f>
-        <v>1214</v>
+        <v>1237</v>
       </c>
       <c r="D18" t="s">
         <v>36</v>
@@ -1976,8 +1976,8 @@
         <v>44378</v>
       </c>
       <c r="C19" s="3">
-        <f>WORKDAY(B19,365)</f>
-        <v>44889</v>
+        <f>WORKDAY(B19,200)</f>
+        <v>44658</v>
       </c>
       <c r="D19" t="s">
         <v>34</v>
